--- a/data/horarios-141-2026-04-11.xlsx
+++ b/data/horarios-141-2026-04-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:26:51</t>
+          <t>Última actualización: 06:06:54</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 3</t>
+          <t>Total filas: 6</t>
         </is>
       </c>
     </row>
@@ -561,6 +561,84 @@
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>06:06:03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>06:08</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>06:06:03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>06:06:03</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>91</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -586,7 +664,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:26:51</t>
+          <t>Última actualización: 06:06:54</t>
         </is>
       </c>
     </row>
@@ -621,7 +699,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:26:51</t>
+          <t>Última actualización: 06:06:54</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-04-11.xlsx
+++ b/data/horarios-141-2026-04-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:06:54</t>
+          <t>Última actualización: 06:57:01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 6</t>
+          <t>Total filas: 7</t>
         </is>
       </c>
     </row>
@@ -639,6 +639,32 @@
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>06:56:11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>11X44_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>90</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -664,7 +690,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:06:54</t>
+          <t>Última actualización: 06:57:01</t>
         </is>
       </c>
     </row>
@@ -699,7 +725,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:06:54</t>
+          <t>Última actualización: 06:57:01</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-04-11.xlsx
+++ b/data/horarios-141-2026-04-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:57:01</t>
+          <t>Última actualización: 07:27:40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 7</t>
+          <t>Total filas: 10</t>
         </is>
       </c>
     </row>
@@ -665,6 +665,84 @@
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>07:26:54</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>14</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>07:26:54</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>24</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>07:26:54</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>98</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -690,7 +768,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:57:01</t>
+          <t>Última actualización: 07:27:40</t>
         </is>
       </c>
     </row>
@@ -712,7 +790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -725,16 +803,74 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:57:01</t>
+          <t>Última actualización: 07:27:40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 0</t>
-        </is>
-      </c>
+          <t>Total filas: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>CodigoColectivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>07:27:40</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>52</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-04-11.xlsx
+++ b/data/horarios-141-2026-04-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:27:40</t>
+          <t>Última actualización: 08:02:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 10</t>
+          <t>Total filas: 15</t>
         </is>
       </c>
     </row>
@@ -743,6 +743,136 @@
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>08:01:57</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>11X44_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>24</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>08:01:57</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>24</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>08:01:57</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>47</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>08:01:57</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>86</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>08:01:57</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>15X38_ABASTO</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>92</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -768,7 +898,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:27:40</t>
+          <t>Última actualización: 08:02:43</t>
         </is>
       </c>
     </row>
@@ -790,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,14 +933,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:27:40</t>
+          <t>Última actualización: 08:02:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 1</t>
+          <t>Total filas: 3</t>
         </is>
       </c>
     </row>
@@ -871,6 +1001,58 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>08:02:43</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>19</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>08:02:43</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>56</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-04-11.xlsx
+++ b/data/horarios-141-2026-04-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:02:43</t>
+          <t>Última actualización: 08:44:59</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 15</t>
+          <t>Total filas: 19</t>
         </is>
       </c>
     </row>
@@ -873,6 +873,110 @@
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>08:44:14</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>08:44:14</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>24</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>08:44:14</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>15X38_ABASTO</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>69</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>08:44:14</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>72</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -885,7 +989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -898,16 +1002,74 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:02:43</t>
+          <t>Última actualización: 08:44:59</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 0</t>
-        </is>
-      </c>
+          <t>Total filas: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>CodigoColectivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>08:44:14</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>72</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -920,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -933,14 +1095,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:02:43</t>
+          <t>Última actualización: 08:44:59</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 3</t>
+          <t>Total filas: 4</t>
         </is>
       </c>
     </row>
@@ -1053,6 +1215,32 @@
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>08:44:59</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>16</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-04-11.xlsx
+++ b/data/horarios-141-2026-04-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:44:59</t>
+          <t>Última actualización: 09:01:33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 19</t>
+          <t>Total filas: 24</t>
         </is>
       </c>
     </row>
@@ -977,6 +977,136 @@
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>09:00:53</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>14X44_ABASTO</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>24</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>09:00:53</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>41</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>09:00:53</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>55</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>09:00:53</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>84</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>09:00:53</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>94</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -989,7 +1119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1002,14 +1132,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:44:59</t>
+          <t>Última actualización: 09:01:33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 1</t>
+          <t>Total filas: 2</t>
         </is>
       </c>
     </row>
@@ -1070,6 +1200,32 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>09:00:53</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>55</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1082,7 +1238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1095,14 +1251,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:44:59</t>
+          <t>Última actualización: 09:01:33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 4</t>
+          <t>Total filas: 8</t>
         </is>
       </c>
     </row>
@@ -1241,6 +1397,110 @@
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>09:01:13</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>76</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>09:01:33</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09:01:33</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>78</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>09:01:33</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>89</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-04-11.xlsx
+++ b/data/horarios-141-2026-04-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 09:01:33</t>
+          <t>Última actualización: 10:22:11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 24</t>
+          <t>Total filas: 29</t>
         </is>
       </c>
     </row>
@@ -1107,6 +1107,136 @@
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>10:21:30</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>10:21:30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>30</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>10:21:30</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>71</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>10:21:30</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>84</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>10:21:30</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>93</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1119,7 +1249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,14 +1262,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 09:01:33</t>
+          <t>Última actualización: 10:22:11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 2</t>
+          <t>Total filas: 3</t>
         </is>
       </c>
     </row>
@@ -1226,6 +1356,32 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>10:21:30</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>84</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1238,7 +1394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1251,14 +1407,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 09:01:33</t>
+          <t>Última actualización: 10:22:11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 8</t>
+          <t>Total filas: 9</t>
         </is>
       </c>
     </row>
@@ -1501,6 +1657,32 @@
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>10:21:51</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>83</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-04-11.xlsx
+++ b/data/horarios-141-2026-04-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:22:11</t>
+          <t>Última actualización: 11:06:15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 29</t>
+          <t>Total filas: 30</t>
         </is>
       </c>
     </row>
@@ -1237,6 +1237,32 @@
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>11:05:29</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>60</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1262,7 +1288,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:22:11</t>
+          <t>Última actualización: 11:06:15</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1407,14 +1433,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:22:11</t>
+          <t>Última actualización: 11:06:15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 9</t>
+          <t>Total filas: 10</t>
         </is>
       </c>
     </row>
@@ -1683,6 +1709,32 @@
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>11:05:50</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>83</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-04-11.xlsx
+++ b/data/horarios-141-2026-04-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:06:15</t>
+          <t>Última actualización: 11:54:57</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 30</t>
+          <t>Total filas: 33</t>
         </is>
       </c>
     </row>
@@ -1263,6 +1263,84 @@
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>11:54:12</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>11:54:12</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>53</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>11:54:12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>62</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1275,7 +1353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1288,14 +1366,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:06:15</t>
+          <t>Última actualización: 11:54:57</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 3</t>
+          <t>Total filas: 4</t>
         </is>
       </c>
     </row>
@@ -1408,6 +1486,32 @@
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>11:54:12</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>62</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1420,7 +1524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1433,14 +1537,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:06:15</t>
+          <t>Última actualización: 11:54:57</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 10</t>
+          <t>Total filas: 11</t>
         </is>
       </c>
     </row>
@@ -1735,6 +1839,32 @@
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>11:54:32</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>61</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-04-11.xlsx
+++ b/data/horarios-141-2026-04-11.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:54:57</t>
+          <t>Última actualización: 12:26:10</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:54:57</t>
+          <t>Última actualización: 12:26:10</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1537,14 +1537,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:54:57</t>
+          <t>Última actualización: 12:26:10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 11</t>
+          <t>Total filas: 12</t>
         </is>
       </c>
     </row>
@@ -1865,6 +1865,32 @@
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>12:25:44</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>36</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-04-11.xlsx
+++ b/data/horarios-141-2026-04-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:26:10</t>
+          <t>Última actualización: 12:54:06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 33</t>
+          <t>Total filas: 34</t>
         </is>
       </c>
     </row>
@@ -1341,6 +1341,32 @@
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>12:53:15</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>49</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1366,7 +1392,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:26:10</t>
+          <t>Última actualización: 12:54:06</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1563,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:26:10</t>
+          <t>Última actualización: 12:54:06</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-04-11.xlsx
+++ b/data/horarios-141-2026-04-11.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:54:06</t>
+          <t>Última actualización: 13:27:28</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:54:06</t>
+          <t>Última actualización: 13:27:28</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1563,14 +1563,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:54:06</t>
+          <t>Última actualización: 13:27:28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 12</t>
+          <t>Total filas: 13</t>
         </is>
       </c>
     </row>
@@ -1917,6 +1917,32 @@
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>13:26:59</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>82</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
